--- a/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1154,6 +1154,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1163,7 +1166,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1474,6 +1477,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1517,7 +1523,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1829,6 +1835,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1838,7 +1847,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2149,6 +2158,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2192,7 +2204,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2504,6 +2516,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2513,7 +2528,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2824,6 +2839,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2846,11 +2864,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="600811008"/>
-        <c:axId val="600812928"/>
+        <c:axId val="546704000"/>
+        <c:axId val="546709888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="600811008"/>
+        <c:axId val="546704000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2893,14 +2911,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="600812928"/>
+        <c:crossAx val="546709888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="600812928"/>
+        <c:axId val="546709888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2949,7 +2967,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="600811008"/>
+        <c:crossAx val="546704000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3134,7 +3152,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3446,6 +3464,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3455,7 +3476,7 @@
               <c:f>'model4(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3766,6 +3787,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3809,7 +3833,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4121,6 +4145,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4130,7 +4157,7 @@
               <c:f>'model4(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4441,6 +4468,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4484,7 +4514,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4796,6 +4826,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4805,7 +4838,7 @@
               <c:f>'model4(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5116,6 +5149,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5138,11 +5174,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="347340160"/>
-        <c:axId val="354034816"/>
+        <c:axId val="546848768"/>
+        <c:axId val="546850304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="347340160"/>
+        <c:axId val="546848768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5185,14 +5221,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="354034816"/>
+        <c:crossAx val="546850304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="354034816"/>
+        <c:axId val="546850304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5241,7 +5277,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="347340160"/>
+        <c:crossAx val="546848768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5426,7 +5462,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5738,6 +5774,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5747,7 +5786,7 @@
               <c:f>'model4(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6058,6 +6097,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6101,7 +6143,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6413,6 +6455,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6422,7 +6467,7 @@
               <c:f>'model4(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6733,6 +6778,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -6776,7 +6824,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7088,6 +7136,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7097,7 +7148,7 @@
               <c:f>'model4(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7408,6 +7459,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7430,11 +7484,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426578688"/>
-        <c:axId val="426580224"/>
+        <c:axId val="546870400"/>
+        <c:axId val="546871936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426578688"/>
+        <c:axId val="546870400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7477,14 +7531,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426580224"/>
+        <c:crossAx val="546871936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426580224"/>
+        <c:axId val="546871936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7533,7 +7587,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426578688"/>
+        <c:crossAx val="546870400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7718,7 +7772,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8030,6 +8084,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8039,7 +8096,7 @@
               <c:f>'model4(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8350,6 +8407,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8393,7 +8453,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8705,6 +8765,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8714,7 +8777,7 @@
               <c:f>'model4(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9025,6 +9088,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9068,7 +9134,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9380,6 +9446,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9389,7 +9458,7 @@
               <c:f>'model4(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9700,6 +9769,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -9722,11 +9794,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426604416"/>
-        <c:axId val="426605952"/>
+        <c:axId val="559200512"/>
+        <c:axId val="559206400"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426604416"/>
+        <c:axId val="559200512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9769,14 +9841,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426605952"/>
+        <c:crossAx val="559206400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426605952"/>
+        <c:axId val="559206400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9825,7 +9897,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426604416"/>
+        <c:crossAx val="559200512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10010,7 +10082,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10322,6 +10394,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10331,7 +10406,7 @@
               <c:f>'model4(3)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10642,6 +10717,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -10685,7 +10763,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10997,6 +11075,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11006,7 +11087,7 @@
               <c:f>'model4(3)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11317,6 +11398,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11360,7 +11444,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11672,6 +11756,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11681,7 +11768,7 @@
               <c:f>'model4(3)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11992,6 +12079,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12014,11 +12104,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426884096"/>
-        <c:axId val="426885888"/>
+        <c:axId val="559832448"/>
+        <c:axId val="559838336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426884096"/>
+        <c:axId val="559832448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12061,14 +12151,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426885888"/>
+        <c:crossAx val="559838336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426885888"/>
+        <c:axId val="559838336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12117,7 +12207,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426884096"/>
+        <c:crossAx val="559832448"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12302,7 +12392,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12614,6 +12704,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12623,7 +12716,7 @@
               <c:f>'model4(3)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12934,6 +13027,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -12977,7 +13073,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13289,6 +13385,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13298,7 +13397,7 @@
               <c:f>'model4(3)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13609,6 +13708,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -13652,7 +13754,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13964,6 +14066,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13973,7 +14078,7 @@
               <c:f>'model4(3)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14284,6 +14389,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14306,11 +14414,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426992000"/>
-        <c:axId val="426993536"/>
+        <c:axId val="559973120"/>
+        <c:axId val="559974656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426992000"/>
+        <c:axId val="559973120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14353,14 +14461,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426993536"/>
+        <c:crossAx val="559974656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426993536"/>
+        <c:axId val="559974656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14409,7 +14517,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426992000"/>
+        <c:crossAx val="559973120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14594,7 +14702,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14906,6 +15014,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14915,7 +15026,7 @@
               <c:f>'model4(3)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15226,6 +15337,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15269,7 +15383,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15581,6 +15695,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15590,7 +15707,7 @@
               <c:f>'model4(3)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15901,6 +16018,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -15944,7 +16064,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16256,6 +16376,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16265,7 +16388,7 @@
               <c:f>'model4(3)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16576,6 +16699,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -16598,11 +16724,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="427173376"/>
-        <c:axId val="427174912"/>
+        <c:axId val="560150400"/>
+        <c:axId val="560151936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="427173376"/>
+        <c:axId val="560150400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16645,14 +16771,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427174912"/>
+        <c:crossAx val="560151936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="427174912"/>
+        <c:axId val="560151936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16701,7 +16827,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427173376"/>
+        <c:crossAx val="560150400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16886,7 +17012,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17198,6 +17324,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17207,7 +17336,7 @@
               <c:f>'model4(3)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17518,6 +17647,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -17561,7 +17693,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17873,6 +18005,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17882,7 +18017,7 @@
               <c:f>'model4(3)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18193,6 +18328,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -18236,7 +18374,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18548,6 +18686,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18557,7 +18698,7 @@
               <c:f>'model4(3)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18868,6 +19009,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -18890,11 +19034,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="486152832"/>
-        <c:axId val="486171008"/>
+        <c:axId val="565181440"/>
+        <c:axId val="593941248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="486152832"/>
+        <c:axId val="565181440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18937,14 +19081,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="486171008"/>
+        <c:crossAx val="593941248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="486171008"/>
+        <c:axId val="593941248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18993,7 +19137,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="486152832"/>
+        <c:crossAx val="565181440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19101,7 +19245,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19144,7 +19288,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19187,7 +19331,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19230,7 +19374,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19273,7 +19417,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19316,7 +19460,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19359,7 +19503,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19402,7 +19546,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19715,7 +19859,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF107"/>
+  <dimension ref="A1:AF108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24153,6 +24297,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="108" spans="1:11" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I108" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J108" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K108" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24171,7 +24350,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -29865,6 +30044,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="108" spans="1:15" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I108" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J108" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K108" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L108" s="26">
+        <v>0.14010746704699642</v>
+      </c>
+      <c r="M108" s="27">
+        <v>0.20675190258530632</v>
+      </c>
+      <c r="N108" s="27">
+        <v>67.765986815617211</v>
+      </c>
+      <c r="O108" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -29883,7 +30109,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -35850,6 +36076,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="108" spans="1:16" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I108" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J108" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K108" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L108" s="26">
+        <v>71.942453334905125</v>
+      </c>
+      <c r="M108" s="27">
+        <v>70.756255946162113</v>
+      </c>
+      <c r="N108" s="27">
+        <v>72.227818114754385</v>
+      </c>
+      <c r="O108" s="27">
+        <v>67.813131608977557</v>
+      </c>
+      <c r="P108" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -35868,7 +36144,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -40945,6 +41221,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="108" spans="1:13" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="20">
+        <v>1994182</v>
+      </c>
+      <c r="E108" s="20">
+        <v>1884119.8412663853</v>
+      </c>
+      <c r="F108" s="21">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>0</v>
+      </c>
+      <c r="I108" s="22">
+        <v>0</v>
+      </c>
+      <c r="J108" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K108" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L108" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M108" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -40963,7 +41280,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF107"/>
+  <dimension ref="A1:AF108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -45401,6 +45718,41 @@
         <v>260.7091440429981</v>
       </c>
     </row>
+    <row r="108" spans="1:11" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I108" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J108" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K108" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -45419,7 +45771,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -51113,6 +51465,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="108" spans="1:15" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="21">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I108" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J108" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K108" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L108" s="26">
+        <v>0.14010746704699642</v>
+      </c>
+      <c r="M108" s="27">
+        <v>0.20675190258530632</v>
+      </c>
+      <c r="N108" s="27">
+        <v>67.765986815617211</v>
+      </c>
+      <c r="O108" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -51131,7 +51530,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -57097,6 +57496,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="108" spans="1:16" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I108" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J108" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K108" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L108" s="26">
+        <v>71.942453334905125</v>
+      </c>
+      <c r="M108" s="27">
+        <v>70.756255946162113</v>
+      </c>
+      <c r="N108" s="27">
+        <v>72.227818114754385</v>
+      </c>
+      <c r="O108" s="27">
+        <v>67.813131608977557</v>
+      </c>
+      <c r="P108" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -57115,7 +57564,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -62192,6 +62641,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="108" spans="1:13" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="20">
+        <v>1994182</v>
+      </c>
+      <c r="E108" s="20">
+        <v>1884119.8412663853</v>
+      </c>
+      <c r="F108" s="21">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>0</v>
+      </c>
+      <c r="I108" s="22">
+        <v>0</v>
+      </c>
+      <c r="J108" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K108" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L108" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M108" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1157,6 +1157,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1166,7 +1169,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1480,6 +1483,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1523,7 +1529,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1838,6 +1844,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1847,7 +1856,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2161,6 +2170,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2204,7 +2216,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2519,6 +2531,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2528,7 +2543,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2842,6 +2857,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2864,11 +2882,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="546704000"/>
-        <c:axId val="546709888"/>
+        <c:axId val="646784896"/>
+        <c:axId val="646881280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="546704000"/>
+        <c:axId val="646784896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2911,14 +2929,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546709888"/>
+        <c:crossAx val="646881280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="546709888"/>
+        <c:axId val="646881280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2967,7 +2985,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546704000"/>
+        <c:crossAx val="646784896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3152,7 +3170,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3467,6 +3485,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3476,7 +3497,7 @@
               <c:f>'model4(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3790,6 +3811,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3833,7 +3857,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4148,6 +4172,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4157,7 +4184,7 @@
               <c:f>'model4(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4471,6 +4498,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4514,7 +4544,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4829,6 +4859,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4838,7 +4871,7 @@
               <c:f>'model4(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5152,6 +5185,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5174,11 +5210,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="546848768"/>
-        <c:axId val="546850304"/>
+        <c:axId val="561709440"/>
+        <c:axId val="561710976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="546848768"/>
+        <c:axId val="561709440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5221,14 +5257,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546850304"/>
+        <c:crossAx val="561710976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="546850304"/>
+        <c:axId val="561710976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5277,7 +5313,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546848768"/>
+        <c:crossAx val="561709440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5462,7 +5498,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5777,6 +5813,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5786,7 +5825,7 @@
               <c:f>'model4(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6100,6 +6139,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6143,7 +6185,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6458,6 +6500,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6467,7 +6512,7 @@
               <c:f>'model4(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6781,6 +6826,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -6824,7 +6872,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7139,6 +7187,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7148,7 +7199,7 @@
               <c:f>'model4(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7462,6 +7513,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7484,11 +7538,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="546870400"/>
-        <c:axId val="546871936"/>
+        <c:axId val="561735168"/>
+        <c:axId val="561736704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="546870400"/>
+        <c:axId val="561735168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7531,14 +7585,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546871936"/>
+        <c:crossAx val="561736704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="546871936"/>
+        <c:axId val="561736704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7587,7 +7641,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546870400"/>
+        <c:crossAx val="561735168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7772,7 +7826,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8087,6 +8141,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8096,7 +8153,7 @@
               <c:f>'model4(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8410,6 +8467,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8453,7 +8513,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8768,6 +8828,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8777,7 +8840,7 @@
               <c:f>'model4(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9091,6 +9154,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9134,7 +9200,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9449,6 +9515,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9458,7 +9527,7 @@
               <c:f>'model4(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9772,6 +9841,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -9794,11 +9866,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559200512"/>
-        <c:axId val="559206400"/>
+        <c:axId val="574098048"/>
+        <c:axId val="574103936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559200512"/>
+        <c:axId val="574098048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9841,14 +9913,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559206400"/>
+        <c:crossAx val="574103936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559206400"/>
+        <c:axId val="574103936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9897,7 +9969,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559200512"/>
+        <c:crossAx val="574098048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10082,7 +10154,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10397,6 +10469,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10406,7 +10481,7 @@
               <c:f>'model4(3)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10720,6 +10795,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -10763,7 +10841,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11078,6 +11156,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11087,7 +11168,7 @@
               <c:f>'model4(3)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11401,6 +11482,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11444,7 +11528,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11759,6 +11843,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11768,7 +11855,7 @@
               <c:f>'model4(3)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12082,6 +12169,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12104,11 +12194,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559832448"/>
-        <c:axId val="559838336"/>
+        <c:axId val="574148608"/>
+        <c:axId val="574150144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559832448"/>
+        <c:axId val="574148608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12151,14 +12241,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559838336"/>
+        <c:crossAx val="574150144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559838336"/>
+        <c:axId val="574150144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12207,7 +12297,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559832448"/>
+        <c:crossAx val="574148608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12392,7 +12482,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12707,6 +12797,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12716,7 +12809,7 @@
               <c:f>'model4(3)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13030,6 +13123,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13073,7 +13169,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13388,6 +13484,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13397,7 +13496,7 @@
               <c:f>'model4(3)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13711,6 +13810,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -13754,7 +13856,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14069,6 +14171,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14078,7 +14183,7 @@
               <c:f>'model4(3)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14392,6 +14497,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14414,11 +14522,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559973120"/>
-        <c:axId val="559974656"/>
+        <c:axId val="574313600"/>
+        <c:axId val="574315136"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559973120"/>
+        <c:axId val="574313600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14461,14 +14569,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559974656"/>
+        <c:crossAx val="574315136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559974656"/>
+        <c:axId val="574315136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14517,7 +14625,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559973120"/>
+        <c:crossAx val="574313600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14702,7 +14810,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15017,6 +15125,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15026,7 +15137,7 @@
               <c:f>'model4(3)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15340,6 +15451,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15383,7 +15497,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15698,6 +15812,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15707,7 +15824,7 @@
               <c:f>'model4(3)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16021,6 +16138,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16064,7 +16184,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16379,6 +16499,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16388,7 +16511,7 @@
               <c:f>'model4(3)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16702,6 +16825,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -16724,11 +16850,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="560150400"/>
-        <c:axId val="560151936"/>
+        <c:axId val="575359232"/>
+        <c:axId val="575361024"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="560150400"/>
+        <c:axId val="575359232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16771,14 +16897,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560151936"/>
+        <c:crossAx val="575361024"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="560151936"/>
+        <c:axId val="575361024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16827,7 +16953,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560150400"/>
+        <c:crossAx val="575359232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17012,7 +17138,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17327,6 +17453,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17336,7 +17465,7 @@
               <c:f>'model4(3)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17650,6 +17779,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -17693,7 +17825,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18008,6 +18140,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18017,7 +18152,7 @@
               <c:f>'model4(3)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18331,6 +18466,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -18374,7 +18512,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18689,6 +18827,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18698,7 +18839,7 @@
               <c:f>'model4(3)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19012,6 +19153,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19034,11 +19178,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="565181440"/>
-        <c:axId val="593941248"/>
+        <c:axId val="575643008"/>
+        <c:axId val="575652992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="565181440"/>
+        <c:axId val="575643008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19081,14 +19225,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="593941248"/>
+        <c:crossAx val="575652992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="593941248"/>
+        <c:axId val="575652992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19137,7 +19281,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565181440"/>
+        <c:crossAx val="575643008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19245,7 +19389,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19288,7 +19432,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19331,7 +19475,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19374,7 +19518,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19417,7 +19561,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19460,7 +19604,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19503,7 +19647,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19546,7 +19690,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19859,7 +20003,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24332,6 +24476,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I109" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J109" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K109" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24350,7 +24529,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30091,6 +30270,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="109" spans="1:15" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I109" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J109" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K109" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L109" s="26">
+        <v>0.15042287299336696</v>
+      </c>
+      <c r="M109" s="27">
+        <v>0.20595990260862521</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.035028220618088</v>
+      </c>
+      <c r="O109" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -30109,7 +30335,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36126,6 +36352,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="109" spans="1:16" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I109" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J109" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K109" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L109" s="26">
+        <v>83.854907882845595</v>
+      </c>
+      <c r="M109" s="27">
+        <v>75.122473258389945</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.192703162632895</v>
+      </c>
+      <c r="O109" s="27">
+        <v>78.982013449904031</v>
+      </c>
+      <c r="P109" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -36144,7 +36420,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41262,6 +41538,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="109" spans="1:13" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="20">
+        <v>1392651</v>
+      </c>
+      <c r="E109" s="20">
+        <v>1884139.3069248656</v>
+      </c>
+      <c r="F109" s="21">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>0</v>
+      </c>
+      <c r="I109" s="22">
+        <v>0</v>
+      </c>
+      <c r="J109" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K109" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L109" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M109" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -41280,7 +41597,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -45753,6 +46070,41 @@
         <v>260.7091440429981</v>
       </c>
     </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I109" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J109" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K109" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -45771,7 +46123,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -51512,6 +51864,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="109" spans="1:15" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="21">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I109" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J109" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K109" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L109" s="26">
+        <v>0.15042287299336696</v>
+      </c>
+      <c r="M109" s="27">
+        <v>0.20595990260862521</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.035028220618088</v>
+      </c>
+      <c r="O109" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -51530,7 +51929,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -57546,6 +57945,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="109" spans="1:16" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I109" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J109" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K109" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L109" s="26">
+        <v>83.854907882845595</v>
+      </c>
+      <c r="M109" s="27">
+        <v>75.122473258389945</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.192703162632895</v>
+      </c>
+      <c r="O109" s="27">
+        <v>78.982013449904031</v>
+      </c>
+      <c r="P109" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -57564,7 +58013,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -62682,6 +63131,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="109" spans="1:13" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="20">
+        <v>1392651</v>
+      </c>
+      <c r="E109" s="20">
+        <v>1884139.3069248656</v>
+      </c>
+      <c r="F109" s="21">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>0</v>
+      </c>
+      <c r="I109" s="22">
+        <v>0</v>
+      </c>
+      <c r="J109" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K109" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L109" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M109" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1160,6 +1160,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1169,7 +1172,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1486,6 +1489,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1529,7 +1535,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1847,6 +1853,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1856,7 +1865,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2173,6 +2182,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2216,7 +2228,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2534,6 +2546,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2543,7 +2558,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2860,6 +2875,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2882,11 +2900,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="646784896"/>
-        <c:axId val="646881280"/>
+        <c:axId val="531904384"/>
+        <c:axId val="543744384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="646784896"/>
+        <c:axId val="531904384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2929,14 +2947,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="646881280"/>
+        <c:crossAx val="543744384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="646881280"/>
+        <c:axId val="543744384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2985,7 +3003,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="646784896"/>
+        <c:crossAx val="531904384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3170,7 +3188,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3488,6 +3506,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3497,7 +3518,7 @@
               <c:f>'model4(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3814,6 +3835,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3857,7 +3881,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4175,6 +4199,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4184,7 +4211,7 @@
               <c:f>'model4(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4501,6 +4528,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4544,7 +4574,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4862,6 +4892,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4871,7 +4904,7 @@
               <c:f>'model4(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5188,6 +5221,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5210,11 +5246,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="561709440"/>
-        <c:axId val="561710976"/>
+        <c:axId val="623975040"/>
+        <c:axId val="691712384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="561709440"/>
+        <c:axId val="623975040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5257,14 +5293,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561710976"/>
+        <c:crossAx val="691712384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="561710976"/>
+        <c:axId val="691712384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5313,7 +5349,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561709440"/>
+        <c:crossAx val="623975040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5498,7 +5534,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5816,6 +5852,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5825,7 +5864,7 @@
               <c:f>'model4(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6142,6 +6181,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6185,7 +6227,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6503,6 +6545,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6512,7 +6557,7 @@
               <c:f>'model4(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6829,6 +6874,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -6872,7 +6920,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7190,6 +7238,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7199,7 +7250,7 @@
               <c:f>'model4(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7516,6 +7567,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7538,11 +7592,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="561735168"/>
-        <c:axId val="561736704"/>
+        <c:axId val="400920960"/>
+        <c:axId val="400922496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="561735168"/>
+        <c:axId val="400920960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7585,14 +7639,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561736704"/>
+        <c:crossAx val="400922496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="561736704"/>
+        <c:axId val="400922496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7641,7 +7695,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561735168"/>
+        <c:crossAx val="400920960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7826,7 +7880,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8144,6 +8198,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8153,7 +8210,7 @@
               <c:f>'model4(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8470,6 +8527,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8513,7 +8573,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8831,6 +8891,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8840,7 +8903,7 @@
               <c:f>'model4(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9157,6 +9220,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9200,7 +9266,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9518,6 +9584,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9527,7 +9596,7 @@
               <c:f>'model4(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9844,6 +9913,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -9866,11 +9938,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574098048"/>
-        <c:axId val="574103936"/>
+        <c:axId val="444757504"/>
+        <c:axId val="444759040"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574098048"/>
+        <c:axId val="444757504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9913,14 +9985,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574103936"/>
+        <c:crossAx val="444759040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574103936"/>
+        <c:axId val="444759040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9969,7 +10041,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574098048"/>
+        <c:crossAx val="444757504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10154,7 +10226,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10472,6 +10544,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10481,7 +10556,7 @@
               <c:f>'model4(3)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10798,6 +10873,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -10841,7 +10919,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11159,6 +11237,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11168,7 +11249,7 @@
               <c:f>'model4(3)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11485,6 +11566,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11528,7 +11612,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11846,6 +11930,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11855,7 +11942,7 @@
               <c:f>'model4(3)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12172,6 +12259,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12194,11 +12284,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574148608"/>
-        <c:axId val="574150144"/>
+        <c:axId val="444779136"/>
+        <c:axId val="444780928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574148608"/>
+        <c:axId val="444779136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12241,14 +12331,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574150144"/>
+        <c:crossAx val="444780928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574150144"/>
+        <c:axId val="444780928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12297,7 +12387,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574148608"/>
+        <c:crossAx val="444779136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12482,7 +12572,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12800,6 +12890,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12809,7 +12902,7 @@
               <c:f>'model4(3)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13126,6 +13219,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13169,7 +13265,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13487,6 +13583,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13496,7 +13595,7 @@
               <c:f>'model4(3)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13813,6 +13912,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -13856,7 +13958,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14174,6 +14276,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14183,7 +14288,7 @@
               <c:f>'model4(3)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14500,6 +14605,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14522,11 +14630,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574313600"/>
-        <c:axId val="574315136"/>
+        <c:axId val="448028672"/>
+        <c:axId val="448030208"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574313600"/>
+        <c:axId val="448028672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14569,14 +14677,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574315136"/>
+        <c:crossAx val="448030208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574315136"/>
+        <c:axId val="448030208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14625,7 +14733,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574313600"/>
+        <c:crossAx val="448028672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14810,7 +14918,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15128,6 +15236,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15137,7 +15248,7 @@
               <c:f>'model4(3)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15454,6 +15565,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15497,7 +15611,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15815,6 +15929,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15824,7 +15941,7 @@
               <c:f>'model4(3)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16141,6 +16258,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16184,7 +16304,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16502,6 +16622,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16511,7 +16634,7 @@
               <c:f>'model4(3)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16828,6 +16951,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -16850,11 +16976,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="575359232"/>
-        <c:axId val="575361024"/>
+        <c:axId val="448103552"/>
+        <c:axId val="448105088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="575359232"/>
+        <c:axId val="448103552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16897,14 +17023,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575361024"/>
+        <c:crossAx val="448105088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="575361024"/>
+        <c:axId val="448105088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16953,7 +17079,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575359232"/>
+        <c:crossAx val="448103552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17138,7 +17264,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17456,6 +17582,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17465,7 +17594,7 @@
               <c:f>'model4(3)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17782,6 +17911,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -17825,7 +17957,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18143,6 +18275,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18152,7 +18287,7 @@
               <c:f>'model4(3)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18469,6 +18604,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -18512,7 +18650,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18830,6 +18968,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18839,7 +18980,7 @@
               <c:f>'model4(3)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19156,6 +19297,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19178,11 +19322,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="575643008"/>
-        <c:axId val="575652992"/>
+        <c:axId val="490133760"/>
+        <c:axId val="492191744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="575643008"/>
+        <c:axId val="490133760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19225,14 +19369,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575652992"/>
+        <c:crossAx val="492191744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="575652992"/>
+        <c:axId val="492191744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19281,7 +19425,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575643008"/>
+        <c:crossAx val="490133760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20003,7 +20147,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24511,6 +24655,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J110" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24529,7 +24708,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30317,6 +30496,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="110" spans="1:15" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J110" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L110" s="26">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="M110" s="27">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N110" s="27">
+        <v>67.892638468724456</v>
+      </c>
+      <c r="O110" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -30335,7 +30561,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36402,6 +36628,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="110" spans="1:16" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J110" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L110" s="26">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="M110" s="27">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="N110" s="27">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="O110" s="27">
+        <v>80.088128126201894</v>
+      </c>
+      <c r="P110" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -36420,7 +36696,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41579,6 +41855,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="110" spans="1:13" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="20">
+        <v>665022</v>
+      </c>
+      <c r="E110" s="20">
+        <v>1877770.3918344665</v>
+      </c>
+      <c r="F110" s="21">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>0</v>
+      </c>
+      <c r="I110" s="22">
+        <v>0</v>
+      </c>
+      <c r="J110" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K110" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L110" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M110" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -41597,7 +41914,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -46105,6 +46422,41 @@
         <v>260.7091440429981</v>
       </c>
     </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I110" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J110" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K110" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -46123,7 +46475,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -51911,6 +52263,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="110" spans="1:15" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="21">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I110" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J110" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K110" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L110" s="26">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="M110" s="27">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N110" s="27">
+        <v>67.892638468724456</v>
+      </c>
+      <c r="O110" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -51929,7 +52328,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -57995,6 +58394,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="110" spans="1:16" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I110" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J110" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K110" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L110" s="26">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="M110" s="27">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="N110" s="27">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="O110" s="27">
+        <v>80.088128126201894</v>
+      </c>
+      <c r="P110" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -58013,7 +58462,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -63172,6 +63621,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="110" spans="1:13" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="20">
+        <v>665022</v>
+      </c>
+      <c r="E110" s="20">
+        <v>1877770.3918344665</v>
+      </c>
+      <c r="F110" s="21">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>0</v>
+      </c>
+      <c r="I110" s="22">
+        <v>0</v>
+      </c>
+      <c r="J110" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K110" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L110" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M110" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1163,6 +1163,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1172,7 +1175,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1492,6 +1495,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1535,7 +1541,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1856,6 +1862,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1865,7 +1874,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2185,6 +2194,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2228,7 +2240,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2549,6 +2561,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2558,7 +2573,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2878,6 +2893,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2900,11 +2918,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="531904384"/>
-        <c:axId val="543744384"/>
+        <c:axId val="399593856"/>
+        <c:axId val="399595392"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="531904384"/>
+        <c:axId val="399593856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2947,14 +2965,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543744384"/>
+        <c:crossAx val="399595392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="543744384"/>
+        <c:axId val="399595392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3003,7 +3021,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531904384"/>
+        <c:crossAx val="399593856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3188,7 +3206,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3509,6 +3527,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3518,7 +3539,7 @@
               <c:f>'model4(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3838,6 +3859,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3881,7 +3905,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4202,6 +4226,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4211,7 +4238,7 @@
               <c:f>'model4(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4531,6 +4558,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4574,7 +4604,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4895,6 +4925,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4904,7 +4937,7 @@
               <c:f>'model4(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5224,6 +5257,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5246,11 +5282,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="623975040"/>
-        <c:axId val="691712384"/>
+        <c:axId val="399611392"/>
+        <c:axId val="399612928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="623975040"/>
+        <c:axId val="399611392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5293,14 +5329,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="691712384"/>
+        <c:crossAx val="399612928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="691712384"/>
+        <c:axId val="399612928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5349,7 +5385,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623975040"/>
+        <c:crossAx val="399611392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5534,7 +5570,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5855,6 +5891,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5864,7 +5903,7 @@
               <c:f>'model4(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6184,6 +6223,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6227,7 +6269,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6548,6 +6590,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6557,7 +6602,7 @@
               <c:f>'model4(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6877,6 +6922,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -6920,7 +6968,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7241,6 +7289,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7250,7 +7301,7 @@
               <c:f>'model4(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7570,6 +7621,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7592,11 +7646,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="400920960"/>
-        <c:axId val="400922496"/>
+        <c:axId val="401234560"/>
+        <c:axId val="401240448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="400920960"/>
+        <c:axId val="401234560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7639,14 +7693,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="400922496"/>
+        <c:crossAx val="401240448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="400922496"/>
+        <c:axId val="401240448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7695,7 +7749,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="400920960"/>
+        <c:crossAx val="401234560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7880,7 +7934,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8201,6 +8255,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8210,7 +8267,7 @@
               <c:f>'model4(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8530,6 +8587,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8573,7 +8633,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8894,6 +8954,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8903,7 +8966,7 @@
               <c:f>'model4(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9223,6 +9286,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9266,7 +9332,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9587,6 +9653,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9596,7 +9665,7 @@
               <c:f>'model4(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9916,6 +9985,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -9938,11 +10010,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="444757504"/>
-        <c:axId val="444759040"/>
+        <c:axId val="401252352"/>
+        <c:axId val="401253888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="444757504"/>
+        <c:axId val="401252352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9985,14 +10057,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444759040"/>
+        <c:crossAx val="401253888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="444759040"/>
+        <c:axId val="401253888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10041,7 +10113,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444757504"/>
+        <c:crossAx val="401252352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10226,7 +10298,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10547,6 +10619,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10556,7 +10631,7 @@
               <c:f>'model4(3)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10876,6 +10951,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -10919,7 +10997,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11240,6 +11318,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11249,7 +11330,7 @@
               <c:f>'model4(3)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11569,6 +11650,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11612,7 +11696,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11933,6 +12017,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11942,7 +12029,7 @@
               <c:f>'model4(3)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12262,6 +12349,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12284,11 +12374,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="444779136"/>
-        <c:axId val="444780928"/>
+        <c:axId val="419390592"/>
+        <c:axId val="419392128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="444779136"/>
+        <c:axId val="419390592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12331,14 +12421,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444780928"/>
+        <c:crossAx val="419392128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="444780928"/>
+        <c:axId val="419392128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12387,7 +12477,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444779136"/>
+        <c:crossAx val="419390592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12572,7 +12662,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12893,6 +12983,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12902,7 +12995,7 @@
               <c:f>'model4(3)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13222,6 +13315,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13265,7 +13361,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13586,6 +13682,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13595,7 +13694,7 @@
               <c:f>'model4(3)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13915,6 +14014,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -13958,7 +14060,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14279,6 +14381,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14288,7 +14393,7 @@
               <c:f>'model4(3)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14608,6 +14713,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14630,11 +14738,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="448028672"/>
-        <c:axId val="448030208"/>
+        <c:axId val="419985664"/>
+        <c:axId val="419987456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="448028672"/>
+        <c:axId val="419985664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14677,14 +14785,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448030208"/>
+        <c:crossAx val="419987456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="448030208"/>
+        <c:axId val="419987456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14733,7 +14841,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448028672"/>
+        <c:crossAx val="419985664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14918,7 +15026,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15239,6 +15347,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15248,7 +15359,7 @@
               <c:f>'model4(3)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15568,6 +15679,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15611,7 +15725,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15932,6 +16046,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15941,7 +16058,7 @@
               <c:f>'model4(3)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16261,6 +16378,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16304,7 +16424,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16625,6 +16745,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16634,7 +16757,7 @@
               <c:f>'model4(3)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16954,6 +17077,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -16976,11 +17102,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="448103552"/>
-        <c:axId val="448105088"/>
+        <c:axId val="420199808"/>
+        <c:axId val="420205696"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="448103552"/>
+        <c:axId val="420199808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17023,14 +17149,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448105088"/>
+        <c:crossAx val="420205696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="448105088"/>
+        <c:axId val="420205696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17079,7 +17205,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448103552"/>
+        <c:crossAx val="420199808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17264,7 +17390,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17585,6 +17711,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17594,7 +17723,7 @@
               <c:f>'model4(3)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17914,6 +18043,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -17957,7 +18089,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18278,6 +18410,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18287,7 +18422,7 @@
               <c:f>'model4(3)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18607,6 +18742,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -18650,7 +18788,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18971,6 +19109,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18980,7 +19121,7 @@
               <c:f>'model4(3)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19300,6 +19441,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19322,11 +19466,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="490133760"/>
-        <c:axId val="492191744"/>
+        <c:axId val="483488512"/>
+        <c:axId val="483490048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="490133760"/>
+        <c:axId val="483488512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19369,14 +19513,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492191744"/>
+        <c:crossAx val="483490048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="492191744"/>
+        <c:axId val="483490048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19425,7 +19569,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="490133760"/>
+        <c:crossAx val="483488512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20147,7 +20291,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF110"/>
+  <dimension ref="A1:AF111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24690,6 +24834,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="111" spans="1:11" ht="12.75">
+      <c r="A111" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.3123262755645897</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I111" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J111" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K111" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24708,7 +24887,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30543,6 +30722,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="111" spans="1:15" ht="12.75">
+      <c r="A111" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.3123262755645897</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I111" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J111" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K111" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L111" s="26">
+        <v>0.10446032846761595</v>
+      </c>
+      <c r="M111" s="27">
+        <v>0.19669438126202543</v>
+      </c>
+      <c r="N111" s="27">
+        <v>53.107937195450262</v>
+      </c>
+      <c r="O111" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -30561,7 +30787,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36678,6 +36904,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="111" spans="1:16" ht="12.75">
+      <c r="A111" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.3123262755645897</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I111" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J111" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K111" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L111" s="26">
+        <v>57.902620211179922</v>
+      </c>
+      <c r="M111" s="27">
+        <v>70.066130263644482</v>
+      </c>
+      <c r="N111" s="27">
+        <v>72.807219335690959</v>
+      </c>
+      <c r="O111" s="27">
+        <v>64.583952119551526</v>
+      </c>
+      <c r="P111" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -36696,7 +36972,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41896,6 +42172,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="111" spans="1:13" ht="12.75">
+      <c r="A111" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.3123262755645897</v>
+      </c>
+      <c r="D111" s="20">
+        <v>534982</v>
+      </c>
+      <c r="E111" s="20">
+        <v>1866104.3575090601</v>
+      </c>
+      <c r="F111" s="21">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>0</v>
+      </c>
+      <c r="I111" s="22">
+        <v>0</v>
+      </c>
+      <c r="J111" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K111" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L111" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M111" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -41914,7 +42231,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF110"/>
+  <dimension ref="A1:AF111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -46457,6 +46774,41 @@
         <v>260.7091440429981</v>
       </c>
     </row>
+    <row r="111" spans="1:11" ht="12.75">
+      <c r="A111" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.3123262755645897</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I111" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J111" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K111" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -46475,7 +46827,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -52310,6 +52662,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="111" spans="1:15" ht="12.75">
+      <c r="A111" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C111" s="21">
+        <v>1.3123262755645897</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I111" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J111" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K111" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L111" s="26">
+        <v>0.10446032846761595</v>
+      </c>
+      <c r="M111" s="27">
+        <v>0.19669438126202543</v>
+      </c>
+      <c r="N111" s="27">
+        <v>53.107937195450262</v>
+      </c>
+      <c r="O111" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -52328,7 +52727,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -58444,6 +58843,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="111" spans="1:16" ht="12.75">
+      <c r="A111" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.3123262755645897</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I111" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J111" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K111" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L111" s="26">
+        <v>57.902620211179922</v>
+      </c>
+      <c r="M111" s="27">
+        <v>70.066130263644482</v>
+      </c>
+      <c r="N111" s="27">
+        <v>72.807219335690959</v>
+      </c>
+      <c r="O111" s="27">
+        <v>64.583952119551526</v>
+      </c>
+      <c r="P111" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -58462,7 +58911,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -63662,6 +64111,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="111" spans="1:13" ht="12.75">
+      <c r="A111" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.3123262755645897</v>
+      </c>
+      <c r="D111" s="20">
+        <v>534982</v>
+      </c>
+      <c r="E111" s="20">
+        <v>1866104.3575090601</v>
+      </c>
+      <c r="F111" s="21">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>0</v>
+      </c>
+      <c r="I111" s="22">
+        <v>0</v>
+      </c>
+      <c r="J111" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K111" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L111" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M111" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1166,6 +1166,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1175,7 +1178,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1498,6 +1501,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1541,7 +1547,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1865,6 +1871,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1874,7 +1883,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2197,6 +2206,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2240,7 +2252,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2564,6 +2576,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2573,7 +2588,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2896,6 +2911,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2918,11 +2936,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399593856"/>
-        <c:axId val="399595392"/>
+        <c:axId val="463945088"/>
+        <c:axId val="463950976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399593856"/>
+        <c:axId val="463945088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2965,14 +2983,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399595392"/>
+        <c:crossAx val="463950976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399595392"/>
+        <c:axId val="463950976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3021,7 +3039,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399593856"/>
+        <c:crossAx val="463945088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3206,7 +3224,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3530,6 +3548,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3539,7 +3560,7 @@
               <c:f>'model4(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3862,6 +3883,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3905,7 +3929,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4229,6 +4253,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4238,7 +4265,7 @@
               <c:f>'model4(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4561,6 +4588,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4604,7 +4634,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4928,6 +4958,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4937,7 +4970,7 @@
               <c:f>'model4(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5260,6 +5293,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5282,11 +5318,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399611392"/>
-        <c:axId val="399612928"/>
+        <c:axId val="463987456"/>
+        <c:axId val="463988992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399611392"/>
+        <c:axId val="463987456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5329,14 +5365,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399612928"/>
+        <c:crossAx val="463988992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399612928"/>
+        <c:axId val="463988992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5385,7 +5421,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399611392"/>
+        <c:crossAx val="463987456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5570,7 +5606,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5894,6 +5930,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5903,7 +5942,7 @@
               <c:f>'model4(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6226,6 +6265,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6269,7 +6311,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6593,6 +6635,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6602,7 +6647,7 @@
               <c:f>'model4(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6925,6 +6970,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -6968,7 +7016,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7292,6 +7340,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7301,7 +7352,7 @@
               <c:f>'model4(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7624,6 +7675,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7646,11 +7700,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401234560"/>
-        <c:axId val="401240448"/>
+        <c:axId val="483846016"/>
+        <c:axId val="483847552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401234560"/>
+        <c:axId val="483846016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7693,14 +7747,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401240448"/>
+        <c:crossAx val="483847552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401240448"/>
+        <c:axId val="483847552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7749,7 +7803,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401234560"/>
+        <c:crossAx val="483846016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7934,7 +7988,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8258,6 +8312,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8267,7 +8324,7 @@
               <c:f>'model4(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8590,6 +8647,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8633,7 +8693,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8957,6 +9017,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8966,7 +9029,7 @@
               <c:f>'model4(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9289,6 +9352,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9332,7 +9398,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9656,6 +9722,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9665,7 +9734,7 @@
               <c:f>'model4(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9988,6 +10057,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -10010,11 +10082,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401252352"/>
-        <c:axId val="401253888"/>
+        <c:axId val="484002816"/>
+        <c:axId val="484016896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401252352"/>
+        <c:axId val="484002816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10057,14 +10129,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401253888"/>
+        <c:crossAx val="484016896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401253888"/>
+        <c:axId val="484016896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10113,7 +10185,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401252352"/>
+        <c:crossAx val="484002816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10298,7 +10370,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10622,6 +10694,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10631,7 +10706,7 @@
               <c:f>'model4(3)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10954,6 +11029,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -10997,7 +11075,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11321,6 +11399,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11330,7 +11411,7 @@
               <c:f>'model4(3)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11653,6 +11734,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11696,7 +11780,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12020,6 +12104,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12029,7 +12116,7 @@
               <c:f>'model4(3)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12352,6 +12439,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12374,11 +12464,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="419390592"/>
-        <c:axId val="419392128"/>
+        <c:axId val="484409728"/>
+        <c:axId val="484411264"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="419390592"/>
+        <c:axId val="484409728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12421,14 +12511,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="419392128"/>
+        <c:crossAx val="484411264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="419392128"/>
+        <c:axId val="484411264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12477,7 +12567,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="419390592"/>
+        <c:crossAx val="484409728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12662,7 +12752,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12986,6 +13076,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12995,7 +13088,7 @@
               <c:f>'model4(3)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13318,6 +13411,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13361,7 +13457,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13685,6 +13781,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13694,7 +13793,7 @@
               <c:f>'model4(3)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14017,6 +14116,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -14060,7 +14162,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14384,6 +14486,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14393,7 +14498,7 @@
               <c:f>'model4(3)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14716,6 +14821,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14738,11 +14846,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="419985664"/>
-        <c:axId val="419987456"/>
+        <c:axId val="528299520"/>
+        <c:axId val="528301056"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="419985664"/>
+        <c:axId val="528299520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14785,14 +14893,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="419987456"/>
+        <c:crossAx val="528301056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="419987456"/>
+        <c:axId val="528301056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14841,7 +14949,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="419985664"/>
+        <c:crossAx val="528299520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15026,7 +15134,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15350,6 +15458,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15359,7 +15470,7 @@
               <c:f>'model4(3)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15682,6 +15793,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15725,7 +15839,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16049,6 +16163,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16058,7 +16175,7 @@
               <c:f>'model4(3)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16381,6 +16498,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16424,7 +16544,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16748,6 +16868,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16757,7 +16880,7 @@
               <c:f>'model4(3)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17080,6 +17203,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -17102,11 +17228,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="420199808"/>
-        <c:axId val="420205696"/>
+        <c:axId val="528726656"/>
+        <c:axId val="528736640"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="420199808"/>
+        <c:axId val="528726656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17149,14 +17275,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="420205696"/>
+        <c:crossAx val="528736640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="420205696"/>
+        <c:axId val="528736640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17205,7 +17331,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="420199808"/>
+        <c:crossAx val="528726656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17390,7 +17516,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17714,6 +17840,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17723,7 +17852,7 @@
               <c:f>'model4(3)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18046,6 +18175,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -18089,7 +18221,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18413,6 +18545,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18422,7 +18557,7 @@
               <c:f>'model4(3)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18745,6 +18880,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -18788,7 +18926,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19112,6 +19250,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19121,7 +19262,7 @@
               <c:f>'model4(3)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19444,6 +19585,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19466,11 +19610,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="483488512"/>
-        <c:axId val="483490048"/>
+        <c:axId val="530759680"/>
+        <c:axId val="530761216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="483488512"/>
+        <c:axId val="530759680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19513,14 +19657,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483490048"/>
+        <c:crossAx val="530761216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483490048"/>
+        <c:axId val="530761216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19569,7 +19713,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483488512"/>
+        <c:crossAx val="530759680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20291,7 +20435,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF111"/>
+  <dimension ref="A1:AF112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24869,6 +25013,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="112" spans="1:11" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I112" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J112" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K112" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24887,7 +25066,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30769,6 +30948,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="112" spans="1:15" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I112" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J112" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K112" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L112" s="26">
+        <v>0.1742169407075714</v>
+      </c>
+      <c r="M112" s="27">
+        <v>0.2510786513695793</v>
+      </c>
+      <c r="N112" s="27">
+        <v>69.387397039635189</v>
+      </c>
+      <c r="O112" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -30787,7 +31013,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36954,6 +37180,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="112" spans="1:16" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I112" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J112" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K112" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L112" s="26">
+        <v>96.669510315522857</v>
+      </c>
+      <c r="M112" s="27">
+        <v>78.933923614270611</v>
+      </c>
+      <c r="N112" s="27">
+        <v>74.84945409521751</v>
+      </c>
+      <c r="O112" s="27">
+        <v>87.102862652376814</v>
+      </c>
+      <c r="P112" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -36972,7 +37248,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -42213,6 +42489,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="112" spans="1:13" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="20">
+        <v>1395013</v>
+      </c>
+      <c r="E112" s="20">
+        <v>1856713.9160601357</v>
+      </c>
+      <c r="F112" s="21">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>0</v>
+      </c>
+      <c r="I112" s="22">
+        <v>0</v>
+      </c>
+      <c r="J112" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K112" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L112" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M112" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -42231,7 +42548,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF111"/>
+  <dimension ref="A1:AF112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -46809,6 +47126,41 @@
         <v>260.7091440429981</v>
       </c>
     </row>
+    <row r="112" spans="1:11" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I112" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J112" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K112" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -46827,7 +47179,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -52709,6 +53061,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="112" spans="1:15" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="21">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I112" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J112" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K112" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L112" s="26">
+        <v>0.1742169407075714</v>
+      </c>
+      <c r="M112" s="27">
+        <v>0.2510786513695793</v>
+      </c>
+      <c r="N112" s="27">
+        <v>69.387397039635189</v>
+      </c>
+      <c r="O112" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -52727,7 +53126,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -58893,6 +59292,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="112" spans="1:16" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I112" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J112" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K112" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L112" s="26">
+        <v>96.669510315522857</v>
+      </c>
+      <c r="M112" s="27">
+        <v>78.933923614270611</v>
+      </c>
+      <c r="N112" s="27">
+        <v>74.84945409521751</v>
+      </c>
+      <c r="O112" s="27">
+        <v>87.102862652376814</v>
+      </c>
+      <c r="P112" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -58911,7 +59360,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -64152,6 +64601,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="112" spans="1:13" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="20">
+        <v>1395013</v>
+      </c>
+      <c r="E112" s="20">
+        <v>1856713.9160601357</v>
+      </c>
+      <c r="F112" s="21">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>0</v>
+      </c>
+      <c r="I112" s="22">
+        <v>0</v>
+      </c>
+      <c r="J112" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K112" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L112" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M112" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1169,6 +1169,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1178,7 +1181,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1504,6 +1507,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1547,7 +1553,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1874,6 +1880,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1883,7 +1892,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2209,6 +2218,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2252,7 +2264,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2579,6 +2591,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2588,7 +2603,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2914,6 +2929,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2936,11 +2954,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="463945088"/>
-        <c:axId val="463950976"/>
+        <c:axId val="473501696"/>
+        <c:axId val="479633408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="463945088"/>
+        <c:axId val="473501696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2983,14 +3001,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463950976"/>
+        <c:crossAx val="479633408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="463950976"/>
+        <c:axId val="479633408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3039,7 +3057,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463945088"/>
+        <c:crossAx val="473501696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3224,7 +3242,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3551,6 +3569,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3560,7 +3581,7 @@
               <c:f>'model4(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3886,6 +3907,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3929,7 +3953,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4256,6 +4280,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4265,7 +4292,7 @@
               <c:f>'model4(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4591,6 +4618,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4634,7 +4664,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4961,6 +4991,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4970,7 +5003,7 @@
               <c:f>'model4(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5296,6 +5329,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5318,11 +5354,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="463987456"/>
-        <c:axId val="463988992"/>
+        <c:axId val="480035968"/>
+        <c:axId val="480037504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="463987456"/>
+        <c:axId val="480035968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5365,14 +5401,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463988992"/>
+        <c:crossAx val="480037504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="463988992"/>
+        <c:axId val="480037504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5421,7 +5457,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463987456"/>
+        <c:crossAx val="480035968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5606,7 +5642,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5933,6 +5969,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5942,7 +5981,7 @@
               <c:f>'model4(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6268,6 +6307,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6311,7 +6353,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6638,6 +6680,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6647,7 +6692,7 @@
               <c:f>'model4(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6973,6 +7018,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -7016,7 +7064,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7343,6 +7391,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7352,7 +7403,7 @@
               <c:f>'model4(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7678,6 +7729,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7700,11 +7754,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="483846016"/>
-        <c:axId val="483847552"/>
+        <c:axId val="524069888"/>
+        <c:axId val="559989504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="483846016"/>
+        <c:axId val="524069888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7747,14 +7801,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483847552"/>
+        <c:crossAx val="559989504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483847552"/>
+        <c:axId val="559989504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7803,7 +7857,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483846016"/>
+        <c:crossAx val="524069888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7988,7 +8042,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8315,6 +8369,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8324,7 +8381,7 @@
               <c:f>'model4(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8650,6 +8707,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8693,7 +8753,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9020,6 +9080,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9029,7 +9092,7 @@
               <c:f>'model4(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9355,6 +9418,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9398,7 +9464,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9725,6 +9791,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9734,7 +9803,7 @@
               <c:f>'model4(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10060,6 +10129,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -10082,11 +10154,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="484002816"/>
-        <c:axId val="484016896"/>
+        <c:axId val="614938880"/>
+        <c:axId val="458747904"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="484002816"/>
+        <c:axId val="614938880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10129,14 +10201,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="484016896"/>
+        <c:crossAx val="458747904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="484016896"/>
+        <c:axId val="458747904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10185,7 +10257,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="484002816"/>
+        <c:crossAx val="614938880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10370,7 +10442,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10697,6 +10769,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10706,7 +10781,7 @@
               <c:f>'model4(3)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11032,6 +11107,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -11075,7 +11153,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11402,6 +11480,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11411,7 +11492,7 @@
               <c:f>'model4(3)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11737,6 +11818,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11780,7 +11864,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12107,6 +12191,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12116,7 +12203,7 @@
               <c:f>'model4(3)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12442,6 +12529,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12464,11 +12554,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="484409728"/>
-        <c:axId val="484411264"/>
+        <c:axId val="465579392"/>
+        <c:axId val="465581184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="484409728"/>
+        <c:axId val="465579392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12511,14 +12601,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="484411264"/>
+        <c:crossAx val="465581184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="484411264"/>
+        <c:axId val="465581184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12567,7 +12657,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="484409728"/>
+        <c:crossAx val="465579392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12752,7 +12842,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13079,6 +13169,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13088,7 +13181,7 @@
               <c:f>'model4(3)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13414,6 +13507,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13457,7 +13553,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13784,6 +13880,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13793,7 +13892,7 @@
               <c:f>'model4(3)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14119,6 +14218,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -14162,7 +14264,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14489,6 +14591,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14498,7 +14603,7 @@
               <c:f>'model4(3)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14824,6 +14929,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14846,11 +14954,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528299520"/>
-        <c:axId val="528301056"/>
+        <c:axId val="465625856"/>
+        <c:axId val="465627392"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528299520"/>
+        <c:axId val="465625856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14893,14 +15001,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528301056"/>
+        <c:crossAx val="465627392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528301056"/>
+        <c:axId val="465627392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14949,7 +15057,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528299520"/>
+        <c:crossAx val="465625856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15134,7 +15242,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15461,6 +15569,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15470,7 +15581,7 @@
               <c:f>'model4(3)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15796,6 +15907,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15839,7 +15953,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16166,6 +16280,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16175,7 +16292,7 @@
               <c:f>'model4(3)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16501,6 +16618,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16544,7 +16664,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16871,6 +16991,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16880,7 +17003,7 @@
               <c:f>'model4(3)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17206,6 +17329,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -17228,11 +17354,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528726656"/>
-        <c:axId val="528736640"/>
+        <c:axId val="467019648"/>
+        <c:axId val="467021184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528726656"/>
+        <c:axId val="467019648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17275,14 +17401,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528736640"/>
+        <c:crossAx val="467021184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528736640"/>
+        <c:axId val="467021184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17331,7 +17457,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528726656"/>
+        <c:crossAx val="467019648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17516,7 +17642,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17843,6 +17969,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17852,7 +17981,7 @@
               <c:f>'model4(3)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18178,6 +18307,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -18221,7 +18353,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18548,6 +18680,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18557,7 +18692,7 @@
               <c:f>'model4(3)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18883,6 +19018,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -18926,7 +19064,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19253,6 +19391,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19262,7 +19403,7 @@
               <c:f>'model4(3)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19588,6 +19729,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19610,11 +19754,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530759680"/>
-        <c:axId val="530761216"/>
+        <c:axId val="467074048"/>
+        <c:axId val="479658752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530759680"/>
+        <c:axId val="467074048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19657,14 +19801,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530761216"/>
+        <c:crossAx val="479658752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530761216"/>
+        <c:axId val="479658752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19713,7 +19857,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530759680"/>
+        <c:crossAx val="467074048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20435,7 +20579,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF112"/>
+  <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25048,6 +25192,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="113" spans="1:11" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I113" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J113" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K113" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -25066,7 +25245,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30995,6 +31174,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="113" spans="1:15" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I113" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J113" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K113" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L113" s="26">
+        <v>0.19018078074406178</v>
+      </c>
+      <c r="M113" s="27">
+        <v>0.25423220629573501</v>
+      </c>
+      <c r="N113" s="27">
+        <v>74.805935689687729</v>
+      </c>
+      <c r="O113" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -31013,7 +31239,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37230,6 +37456,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="113" spans="1:16" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I113" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J113" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K113" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L113" s="26">
+        <v>86.321154877675269</v>
+      </c>
+      <c r="M113" s="27">
+        <v>81.396334035405502</v>
+      </c>
+      <c r="N113" s="27">
+        <v>77.031747408613512</v>
+      </c>
+      <c r="O113" s="27">
+        <v>90.125507288989468</v>
+      </c>
+      <c r="P113" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -37248,7 +37524,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -42530,6 +42806,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="113" spans="1:13" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="20">
+        <v>1204034</v>
+      </c>
+      <c r="E113" s="20">
+        <v>1851506.4082384438</v>
+      </c>
+      <c r="F113" s="21">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>0</v>
+      </c>
+      <c r="I113" s="22">
+        <v>0</v>
+      </c>
+      <c r="J113" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K113" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L113" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M113" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -42548,7 +42865,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF112"/>
+  <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -47161,6 +47478,41 @@
         <v>260.7091440429981</v>
       </c>
     </row>
+    <row r="113" spans="1:11" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I113" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J113" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K113" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -47179,7 +47531,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -53108,6 +53460,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="113" spans="1:15" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="21">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I113" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J113" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K113" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L113" s="26">
+        <v>0.19018078074406178</v>
+      </c>
+      <c r="M113" s="27">
+        <v>0.25423220629573501</v>
+      </c>
+      <c r="N113" s="27">
+        <v>74.805935689687729</v>
+      </c>
+      <c r="O113" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -53126,7 +53525,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -59342,6 +59741,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="113" spans="1:16" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I113" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J113" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K113" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L113" s="26">
+        <v>86.321154877675269</v>
+      </c>
+      <c r="M113" s="27">
+        <v>81.396334035405502</v>
+      </c>
+      <c r="N113" s="27">
+        <v>77.031747408613512</v>
+      </c>
+      <c r="O113" s="27">
+        <v>90.125507288989468</v>
+      </c>
+      <c r="P113" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -59360,7 +59809,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -64642,6 +65091,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="113" spans="1:13" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="20">
+        <v>1204034</v>
+      </c>
+      <c r="E113" s="20">
+        <v>1851506.4082384438</v>
+      </c>
+      <c r="F113" s="21">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>0</v>
+      </c>
+      <c r="I113" s="22">
+        <v>0</v>
+      </c>
+      <c r="J113" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K113" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L113" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M113" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
